--- a/Metadane.xlsx
+++ b/Metadane.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\s180030\Analiza danych R i Python\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cbd9db93bb972cc2/Pulpit/studia/analityka/semestr 3/Analiza danych python/Analiza-danych/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6CAAC4C3-8FEB-40F3-9850-4D4501CD078F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{6CAAC4C3-8FEB-40F3-9850-4D4501CD078F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19289F85-041C-4101-A862-2315E7983366}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11505" xr2:uid="{C570FC65-7A65-48AC-87F4-6796F297D1B8}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C570FC65-7A65-48AC-87F4-6796F297D1B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -217,7 +217,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -230,6 +230,15 @@
       <b/>
       <sz val="14"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
@@ -396,10 +405,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -419,15 +429,19 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperłącze" xfId="1" builtinId="8"/>
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -444,9 +458,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motyw pakietu Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motyw pakietu Office 2013–2022">
   <a:themeElements>
-    <a:clrScheme name="Pakiet Office">
+    <a:clrScheme name="Pakiet Office 2013–2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -484,7 +498,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Pakiet Office">
+    <a:fontScheme name="Pakiet Office 2013–2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -590,7 +604,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Pakiet Office">
+    <a:fmtScheme name="Pakiet Office 2013–2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -732,7 +746,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -741,882 +755,882 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C73ABFE4-6C12-432A-9856-A5CBD020D167}">
   <dimension ref="A1:B110"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="111.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="111.81640625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:2" ht="19" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="7"/>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="B1" s="11"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="8" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="3">
         <v>2024</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="8" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="8" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="8" t="s">
         <v>15</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="8" t="s">
         <v>17</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="8" t="s">
         <v>19</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="10" t="s">
+    <row r="13" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="9" t="s">
         <v>21</v>
       </c>
       <c r="B13" s="5">
         <v>45782</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="8" t="s">
         <v>4</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B17" s="3">
         <v>2024</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="8" t="s">
         <v>7</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="8" t="s">
         <v>9</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="8" t="s">
         <v>11</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="8" t="s">
         <v>15</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="8" t="s">
         <v>17</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="8" t="s">
         <v>19</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="11" t="s">
+    <row r="25" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="10" t="s">
         <v>21</v>
       </c>
       <c r="B25" s="6">
         <v>45841</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="9" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="8" t="s">
         <v>4</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="9" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B29" s="3">
         <v>2024</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="9" t="s">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="8" t="s">
         <v>7</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="9" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" s="8" t="s">
         <v>9</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="9" t="s">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" s="8" t="s">
         <v>11</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="9" t="s">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="9" t="s">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" s="8" t="s">
         <v>15</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="9" t="s">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" s="8" t="s">
         <v>17</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="9" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" s="8" t="s">
         <v>19</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="11" t="s">
+    <row r="37" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="10" t="s">
         <v>21</v>
       </c>
       <c r="B37" s="6">
         <v>45826</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="8" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="9" t="s">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="9" t="s">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" s="8" t="s">
         <v>4</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="9" t="s">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B41" s="3">
         <v>2024</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="9" t="s">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" s="8" t="s">
         <v>7</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="9" t="s">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" s="8" t="s">
         <v>9</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="9" t="s">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" s="8" t="s">
         <v>11</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="9" t="s">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="9" t="s">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" s="8" t="s">
         <v>15</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="9" t="s">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" s="8" t="s">
         <v>17</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="9" t="s">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" s="8" t="s">
         <v>19</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="9"/>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" s="8"/>
       <c r="B49" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="11" t="s">
+    <row r="50" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="10" t="s">
         <v>21</v>
       </c>
       <c r="B50" s="6">
         <v>45854</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="8" t="s">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="9" t="s">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="9" t="s">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53" s="8" t="s">
         <v>4</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="9" t="s">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B54" s="3">
         <v>2024</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="9" t="s">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A55" s="8" t="s">
         <v>7</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="9" t="s">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A56" s="8" t="s">
         <v>9</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="9" t="s">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A57" s="8" t="s">
         <v>11</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="9" t="s">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A58" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="9" t="s">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A59" s="8" t="s">
         <v>15</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="9" t="s">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A60" s="8" t="s">
         <v>17</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="9" t="s">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A61" s="8" t="s">
         <v>19</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="11" t="s">
+    <row r="62" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A62" s="10" t="s">
         <v>21</v>
       </c>
       <c r="B62" s="6">
         <v>45840</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="8" t="s">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A63" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="9" t="s">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A64" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="9" t="s">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A65" s="8" t="s">
         <v>4</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="9" t="s">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A66" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B66" s="3">
         <v>2024</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="9" t="s">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A67" s="8" t="s">
         <v>7</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="9" t="s">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A68" s="8" t="s">
         <v>9</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="9" t="s">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A69" s="8" t="s">
         <v>11</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="9" t="s">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A70" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="9" t="s">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A71" s="8" t="s">
         <v>15</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="9" t="s">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A72" s="8" t="s">
         <v>17</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="9" t="s">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A73" s="8" t="s">
         <v>19</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="11" t="s">
+    <row r="74" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A74" s="10" t="s">
         <v>21</v>
       </c>
       <c r="B74" s="6">
         <v>45677</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" s="8" t="s">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A75" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" s="9" t="s">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A76" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" s="9" t="s">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A77" s="8" t="s">
         <v>4</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" s="9" t="s">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A78" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B78" s="3">
         <v>2024</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" s="9" t="s">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A79" s="8" t="s">
         <v>7</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" s="9" t="s">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A80" s="8" t="s">
         <v>9</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" s="9" t="s">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A81" s="8" t="s">
         <v>11</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" s="9" t="s">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A82" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" s="9" t="s">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A83" s="8" t="s">
         <v>15</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" s="9" t="s">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A84" s="8" t="s">
         <v>17</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" s="9" t="s">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A85" s="8" t="s">
         <v>19</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="86" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="11" t="s">
+    <row r="86" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A86" s="10" t="s">
         <v>21</v>
       </c>
       <c r="B86" s="6">
         <v>45677</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" s="8" t="s">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A87" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" s="9" t="s">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A88" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" s="9" t="s">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A89" s="8" t="s">
         <v>4</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90" s="9" t="s">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A90" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B90" s="3">
         <v>2024</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A91" s="9" t="s">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A91" s="8" t="s">
         <v>7</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A92" s="9" t="s">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A92" s="8" t="s">
         <v>9</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A93" s="9" t="s">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A93" s="8" t="s">
         <v>11</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A94" s="9" t="s">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A94" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A95" s="9" t="s">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A95" s="8" t="s">
         <v>15</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A96" s="9" t="s">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A96" s="8" t="s">
         <v>17</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A97" s="9" t="s">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A97" s="8" t="s">
         <v>19</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="98" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="11" t="s">
+    <row r="98" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A98" s="10" t="s">
         <v>21</v>
       </c>
       <c r="B98" s="6">
         <v>45869</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A99" s="8" t="s">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A99" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A100" s="9" t="s">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A100" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B100" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A101" s="9" t="s">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A101" s="8" t="s">
         <v>4</v>
       </c>
       <c r="B101" s="4" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A102" s="9" t="s">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A102" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B102" s="3">
         <v>2025</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A103" s="9" t="s">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A103" s="8" t="s">
         <v>7</v>
       </c>
       <c r="B103" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A104" s="9" t="s">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A104" s="8" t="s">
         <v>9</v>
       </c>
       <c r="B104" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A105" s="9" t="s">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A105" s="8" t="s">
         <v>11</v>
       </c>
       <c r="B105" s="3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A106" s="9" t="s">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A106" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A107" s="9" t="s">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A107" s="8" t="s">
         <v>15</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A108" s="9" t="s">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A108" s="8" t="s">
         <v>17</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A109" s="9" t="s">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A109" s="8" t="s">
         <v>19</v>
       </c>
       <c r="B109" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="110" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="10" t="s">
+    <row r="110" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A110" s="9" t="s">
         <v>21</v>
       </c>
       <c r="B110" s="5">
@@ -1627,7 +1641,10 @@
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="B8" r:id="rId1" xr:uid="{E3EE58C4-8D1C-47CE-AA9F-CF083A9ABFE9}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>